--- a/app/components/ריכוז ספקים.xlsx
+++ b/app/components/ריכוז ספקים.xlsx
@@ -106,8 +106,33 @@
           <t xml:space="preserve">ריכוז ספקים</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">שם פרויקט</t>
@@ -130,16 +155,16 @@
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">הבטחת איכות</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t xml:space="preserve">תיקו הנדסה אזרחית</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">בקרת איכות</t>
@@ -152,54 +177,74 @@
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">הבטחת איכות</t>
+          <t xml:space="preserve">שם הקבלן</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">תיקו הנדסה אזרחית</t>
+          <t xml:space="preserve">מפלסי הגליל סלילה עפר ופיתוח בע"מ</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">מקור נתונים</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">בקרה מקדימה / ספקים</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">מקור נתונים</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">בקרה מקדימה / ספקים</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">שם הקבלן</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">מפלסי הגליל סלילה עפר ופיתוח בע"מ</t>
+      <c r="A4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="0">
+        <is>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
@@ -556,5 +601,8 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
 </worksheet>
 </file>
--- a/app/components/ריכוז ספקים.xlsx
+++ b/app/components/ריכוז ספקים.xlsx
@@ -127,7 +127,7 @@
     <col min="9" max="9" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">ריכוז ספקים</t>
@@ -164,11 +164,6 @@
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -177,7 +172,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">שם פרויקט</t>
+          <t xml:space="preserve">שם פרויקט:</t>
         </is>
       </c>
       <c r="B2" t="inlineStr" s="2">
@@ -187,173 +182,227 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">ניהול פרויקט</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="2">
+      <c r="F2" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">א. ש. רונן הנדסה אזרחית בע"מ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">קבלן</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">מפלסי הגליל סלילה עפר ופיתוח בע"מ</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">בקרת איכות</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">קונטרולינג פריים בע"מ</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">שם הקבלן</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">מפלסי הגליל סלילה עפר ופיתוח בע"מ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">הבטחת איכות</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="2">
+      <c r="F3" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">תיקו הנדסה אזרחית</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">מנהל עבודה</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">חוסיין מריסאת</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">מודד</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">באסל אבו שקארה</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">מפקח</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">עאמר והיב</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" t="inlineStr" s="3">
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">בקרת איכות</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">קונטרולינג פריים בע"מ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">מקור נתונים</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">בקרה מקדימה / ספקים</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1"/>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">מס׳</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr" s="3">
+      <c r="B6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">שם ספק</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr" s="3">
+      <c r="C6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">חומר/מוצר מסופק</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="3">
+      <c r="D6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">תאריך אישור</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr" s="3">
+      <c r="E6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">מספר תעודה / רישיון / אישור</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr" s="3">
+      <c r="F6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">סוג תעודה /ISO/ת״ת/רישיון</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr" s="3">
+      <c r="G6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">סטטוס</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr" s="3">
+      <c r="H6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">תוקף</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr" s="3">
+      <c r="I6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">הערות</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5">
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr" s="5">
+      <c r="B7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">אליהו תעשיות פלסיק בע"מ</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="5">
+      <c r="C7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">מובילי פלסטיק למתקני חשמל ותקשורת</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="5">
+      <c r="D7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">24/04/2026</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr" s="5">
+      <c r="E7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">97252</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr" s="5">
+      <c r="F7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">ISO</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr" s="5">
+      <c r="G7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">מאושר</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr" s="5">
+      <c r="H7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">06/05/2028</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr" s="5">
+      <c r="I7" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+  <mergeCells count="13">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/app/components/ריכוז ספקים.xlsx
+++ b/app/components/ריכוז ספקים.xlsx
@@ -116,293 +116,554 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="22" customWidth="1"/>
-    <col min="9" max="9" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="11" customWidth="1"/>
+    <col min="14" max="14" width="11" customWidth="1"/>
+    <col min="15" max="15" width="11" customWidth="1"/>
+    <col min="16" max="16" width="11" customWidth="1"/>
+    <col min="17" max="17" width="11" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="11" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="11" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="18" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="18" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" t="inlineStr" s="1">
+    <row r="1" ht="14" customHeight="1"/>
+    <row r="2" ht="20" customHeight="1">
+      <c r="H2" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">ריכוז ספקים</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="2" ht="22" customHeight="1">
-      <c r="A2" t="inlineStr" s="2">
+    <row r="3" ht="18" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="H4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">שם פרויקט:</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr" s="2">
+      <c r="I4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">כביש 806 צלמון שלב א׳</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr" s="2">
+      <c r="K4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="H5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">ניהול פרויקט</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr" s="2">
+      <c r="I5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">א. ש. רונן הנדסה אזרחית בע"מ</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr" s="2">
+      <c r="K5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" t="inlineStr" s="2">
+    <row r="6" ht="20" customHeight="1">
+      <c r="H6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">שם הקבלן</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr" s="2">
+      <c r="I6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">מפלסי הגליל סלילה עפר ופיתוח בע"מ</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">הבטחת איכות</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">תיקו הנדסה אזרחית</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr" s="2">
+      <c r="K6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">בקרת איכות</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">קונטרולינג פריים בע"מ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">מקור נתונים</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">בקרה מקדימה / ספקים</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr" s="2">
+    <row r="7" ht="20" customHeight="1">
+      <c r="H7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">בקרת איכות - קונטרולינג פריים בע"מ</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">הבטחת איכות - תיקו הנדסה אזרחית</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1"/>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" t="inlineStr" s="3">
+    <row r="8" ht="16" customHeight="1"/>
+    <row r="9" ht="16" customHeight="1"/>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">מס׳</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr" s="3">
+      <c r="B10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">שם ספק</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr" s="3">
+      <c r="C10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">חומר/מוצר מסופק</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="3">
+      <c r="D10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">תאריך אישור</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr" s="3">
+      <c r="E10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">מספר תעודה / רישיון / אישור</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr" s="3">
+      <c r="F10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">סוג תעודה /ISO/ת״ת/רישיון</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr" s="3">
+      <c r="G10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">סטטוס</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr" s="3">
+      <c r="H10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">תוקף</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr" s="3">
+      <c r="I10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">הערות</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="6">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr" s="6">
+      <c r="B11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">אליהו תעשיות פלסיק בע"מ</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr" s="6">
+      <c r="C11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">מובילי פלסטיק למתקני חשמל ותקשורת</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="6">
+      <c r="D11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">24/04/2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr" s="6">
+      <c r="E11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">97252</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr" s="6">
+      <c r="F11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">ISO</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr" s="6">
+      <c r="G11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">מאושר</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr" s="6">
+      <c r="H11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">06/05/2028</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr" s="6">
+      <c r="I11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr" s="6">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+  <mergeCells count="9">
+    <mergeCell ref="H2:O2"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:O6"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="L7:O7"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/app/components/ריכוז ספקים.xlsx
+++ b/app/components/ריכוז ספקים.xlsx
@@ -125,26 +125,13 @@
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="14" width="11" customWidth="1"/>
-    <col min="15" max="15" width="11" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11" customWidth="1"/>
-    <col min="18" max="18" width="11" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="11" customWidth="1"/>
-    <col min="23" max="23" width="11" customWidth="1"/>
-    <col min="24" max="24" width="18" customWidth="1"/>
-    <col min="25" max="25" width="18" customWidth="1"/>
-    <col min="26" max="26" width="18" customWidth="1"/>
-    <col min="27" max="27" width="18" customWidth="1"/>
-    <col min="28" max="28" width="18" customWidth="1"/>
-    <col min="29" max="29" width="18" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14" customHeight="1"/>
@@ -362,292 +349,92 @@
     <row r="8" ht="16" customHeight="1"/>
     <row r="9" ht="16" customHeight="1"/>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" t="inlineStr" s="3">
+      <c r="H10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">מס׳</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr" s="3">
+      <c r="I10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">שם ספק</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr" s="3">
+      <c r="J10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">חומר/מוצר מסופק</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="3">
+      <c r="K10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">תאריך אישור</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr" s="3">
+      <c r="L10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">מספר תעודה / רישיון / אישור</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr" s="3">
+      <c r="M10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">סוג תעודה /ISO/ת״ת/רישיון</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr" s="3">
+      <c r="N10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">סטטוס</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr" s="3">
+      <c r="O10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">תוקף</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr" s="3">
+      <c r="P10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">הערות</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="6">
+      <c r="H11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" t="inlineStr" s="6">
+      <c r="I11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">אליהו תעשיות פלסיק בע"מ</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr" s="6">
+      <c r="J11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">מובילי פלסטיק למתקני חשמל ותקשורת</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="6">
+      <c r="K11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">24/04/2026</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr" s="6">
+      <c r="L11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">97252</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr" s="6">
+      <c r="M11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">ISO</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr" s="6">
+      <c r="N11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">מאושר</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr" s="6">
+      <c r="O11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve">06/05/2028</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="P11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr" s="6">
         <is>
           <t xml:space="preserve"/>
         </is>
